--- a/data/trade_log_us.xlsx
+++ b/data/trade_log_us.xlsx
@@ -431,61 +431,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>SMA20</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Upper_Band</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>EMA9</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>EMA21</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Vol_Ratio</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Qualifies</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Rejection_Or_Status</t>
         </is>
@@ -1864,6 +1864,694 @@
       <c r="K33" t="inlineStr">
         <is>
           <t>BELOW_BAND (Close 168.57 &lt;= Upper 169.98)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>10:52:57</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>224.41</v>
+      </c>
+      <c r="E34" t="n">
+        <v>229.99</v>
+      </c>
+      <c r="F34" t="n">
+        <v>229.99</v>
+      </c>
+      <c r="G34" t="n">
+        <v>219.16</v>
+      </c>
+      <c r="H34" t="n">
+        <v>216.86</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="J34" t="b">
+        <v>0</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 224.41 &lt;= Upper 229.99)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>10:52:57</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>357.01</v>
+      </c>
+      <c r="E35" t="n">
+        <v>369.45</v>
+      </c>
+      <c r="F35" t="n">
+        <v>369.45</v>
+      </c>
+      <c r="G35" t="n">
+        <v>353.61</v>
+      </c>
+      <c r="H35" t="n">
+        <v>348.93</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J35" t="b">
+        <v>0</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 357.01 &lt;= Upper 369.45)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>10:52:57</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>324.96</v>
+      </c>
+      <c r="E36" t="n">
+        <v>324.62</v>
+      </c>
+      <c r="F36" t="n">
+        <v>324.62</v>
+      </c>
+      <c r="G36" t="n">
+        <v>317.92</v>
+      </c>
+      <c r="H36" t="n">
+        <v>315.22</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J36" t="b">
+        <v>0</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>LOW_VOLUME (VolRatio 0.85x &lt; 1.3x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>10:52:57</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>496.82</v>
+      </c>
+      <c r="E37" t="n">
+        <v>514.35</v>
+      </c>
+      <c r="F37" t="n">
+        <v>514.35</v>
+      </c>
+      <c r="G37" t="n">
+        <v>498.32</v>
+      </c>
+      <c r="H37" t="n">
+        <v>485.33</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="J37" t="b">
+        <v>0</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 496.82 &lt;= Upper 514.35)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>10:52:57</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>592.85</v>
+      </c>
+      <c r="E38" t="n">
+        <v>610.46</v>
+      </c>
+      <c r="F38" t="n">
+        <v>610.46</v>
+      </c>
+      <c r="G38" t="n">
+        <v>575.91</v>
+      </c>
+      <c r="H38" t="n">
+        <v>577.25</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="J38" t="b">
+        <v>0</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 575.91 &lt;= EMA21 577.25)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>10:52:57</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>254.98</v>
+      </c>
+      <c r="E39" t="n">
+        <v>276.69</v>
+      </c>
+      <c r="F39" t="n">
+        <v>276.69</v>
+      </c>
+      <c r="G39" t="n">
+        <v>259.12</v>
+      </c>
+      <c r="H39" t="n">
+        <v>259.71</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="J39" t="b">
+        <v>0</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 259.12 &lt;= EMA21 259.71)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>10:52:57</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>337.12</v>
+      </c>
+      <c r="E40" t="n">
+        <v>357.04</v>
+      </c>
+      <c r="F40" t="n">
+        <v>357.04</v>
+      </c>
+      <c r="G40" t="n">
+        <v>341.03</v>
+      </c>
+      <c r="H40" t="n">
+        <v>344.26</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="J40" t="b">
+        <v>0</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 341.03 &lt;= EMA21 344.26)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>10:52:57</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>457.06</v>
+      </c>
+      <c r="E41" t="n">
+        <v>506.53</v>
+      </c>
+      <c r="F41" t="n">
+        <v>506.53</v>
+      </c>
+      <c r="G41" t="n">
+        <v>468.41</v>
+      </c>
+      <c r="H41" t="n">
+        <v>477.21</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J41" t="b">
+        <v>0</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 468.41 &lt;= EMA21 477.21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>10:52:57</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>82.73</v>
+      </c>
+      <c r="E42" t="n">
+        <v>84.45</v>
+      </c>
+      <c r="F42" t="n">
+        <v>84.45</v>
+      </c>
+      <c r="G42" t="n">
+        <v>80.84</v>
+      </c>
+      <c r="H42" t="n">
+        <v>78.87</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J42" t="b">
+        <v>0</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 82.73 &lt;= Upper 84.45)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>10:52:57</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>169.46</v>
+      </c>
+      <c r="E43" t="n">
+        <v>189.15</v>
+      </c>
+      <c r="F43" t="n">
+        <v>189.15</v>
+      </c>
+      <c r="G43" t="n">
+        <v>177.82</v>
+      </c>
+      <c r="H43" t="n">
+        <v>170.64</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="J43" t="b">
+        <v>0</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 169.46 &lt;= Upper 189.15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>10:52:57</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>367.24</v>
+      </c>
+      <c r="E44" t="n">
+        <v>436.13</v>
+      </c>
+      <c r="F44" t="n">
+        <v>436.13</v>
+      </c>
+      <c r="G44" t="n">
+        <v>369.6</v>
+      </c>
+      <c r="H44" t="n">
+        <v>377.6</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="J44" t="b">
+        <v>0</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 369.60 &lt;= EMA21 377.60)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>10:52:57</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>COIN</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>174.96</v>
+      </c>
+      <c r="E45" t="n">
+        <v>199.72</v>
+      </c>
+      <c r="F45" t="n">
+        <v>199.72</v>
+      </c>
+      <c r="G45" t="n">
+        <v>177.74</v>
+      </c>
+      <c r="H45" t="n">
+        <v>170.79</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J45" t="b">
+        <v>0</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 174.96 &lt;= Upper 199.72)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>10:52:57</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ARM</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>234.86</v>
+      </c>
+      <c r="E46" t="n">
+        <v>291.51</v>
+      </c>
+      <c r="F46" t="n">
+        <v>291.51</v>
+      </c>
+      <c r="G46" t="n">
+        <v>243.36</v>
+      </c>
+      <c r="H46" t="n">
+        <v>253.29</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="J46" t="b">
+        <v>0</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 243.36 &lt;= EMA21 253.29)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>10:52:57</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>76.45</v>
+      </c>
+      <c r="E47" t="n">
+        <v>81.31</v>
+      </c>
+      <c r="F47" t="n">
+        <v>81.31</v>
+      </c>
+      <c r="G47" t="n">
+        <v>76.92</v>
+      </c>
+      <c r="H47" t="n">
+        <v>76.16</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J47" t="b">
+        <v>0</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 76.45 &lt;= Upper 81.31)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>10:52:57</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>37</v>
+      </c>
+      <c r="E48" t="n">
+        <v>42.04</v>
+      </c>
+      <c r="F48" t="n">
+        <v>42.04</v>
+      </c>
+      <c r="G48" t="n">
+        <v>37.02</v>
+      </c>
+      <c r="H48" t="n">
+        <v>35.65</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="J48" t="b">
+        <v>0</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 37.00 &lt;= Upper 42.04)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>10:52:57</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>QCOM</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>169.96</v>
+      </c>
+      <c r="E49" t="n">
+        <v>170.12</v>
+      </c>
+      <c r="F49" t="n">
+        <v>170.12</v>
+      </c>
+      <c r="G49" t="n">
+        <v>165.72</v>
+      </c>
+      <c r="H49" t="n">
+        <v>165.03</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="J49" t="b">
+        <v>0</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 169.96 &lt;= Upper 170.12)</t>
         </is>
       </c>
     </row>
@@ -1991,104 +2679,63 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Entry_Date</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Entry_Price</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Invested</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Current_Price</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Unrealized_PnL_Pct</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Hard_SL</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Highest_High</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Days_Held</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>TSLA</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>376.37</v>
-      </c>
-      <c r="D2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1881.85</v>
-      </c>
-      <c r="F2" t="n">
-        <v>376.37</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>359.43</v>
-      </c>
-      <c r="I2" t="n">
-        <v>384.0400085449219</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>OPEN</t>
         </is>
       </c>
     </row>
@@ -2103,71 +2750,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Entry_Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Exit_Date</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Entry_Price</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Exit_Price</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Invested</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Gross_PnL_Pct</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Net_PnL_Pct</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>PnL_Amount</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Exit_Reason</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Days_Held</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2219,6 +2866,57 @@
         <v>2</v>
       </c>
       <c r="M2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>376.37</v>
+      </c>
+      <c r="E3" t="n">
+        <v>359.43</v>
+      </c>
+      <c r="F3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1881.85</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-4.501</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-4.551</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-85.64</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>HARD_STOP_LOSS</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -2235,61 +2933,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Timestamp</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Order_ID</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Side</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Expected_Price</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Fill_Price</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Slippage</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -2390,6 +3088,55 @@
       <c r="K3" t="inlineStr">
         <is>
           <t>Entry Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-04 10:52:56</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>44F68F0F13</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>359.43</v>
+      </c>
+      <c r="G4" t="n">
+        <v>359.43</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>FILLED</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>HARD_STOP_LOSS</t>
         </is>
       </c>
     </row>
@@ -2408,27 +3155,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Timestamp</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Details</t>
         </is>
@@ -2472,51 +3219,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Cash_Available</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Invested_Capital</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Total_Equity</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Realized_PnL</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Win_Rate_Pct</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Total_Trades</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Open_Positions</t>
         </is>
@@ -2586,6 +3333,39 @@
       </c>
       <c r="I3" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>10:52:57</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>9828.719999999999</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>9828.719999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-171.28</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/trade_log_us.xlsx
+++ b/data/trade_log_us.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K49"/>
+  <dimension ref="A1:K65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2552,6 +2552,694 @@
       <c r="K49" t="inlineStr">
         <is>
           <t>BELOW_BAND (Close 169.96 &lt;= Upper 170.12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>04:26:39</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>230.36</v>
+      </c>
+      <c r="E50" t="n">
+        <v>232.35</v>
+      </c>
+      <c r="F50" t="n">
+        <v>232.35</v>
+      </c>
+      <c r="G50" t="n">
+        <v>222.89</v>
+      </c>
+      <c r="H50" t="n">
+        <v>219.04</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="J50" t="b">
+        <v>0</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 230.36 &lt;= Upper 232.35)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>04:26:39</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>354.08</v>
+      </c>
+      <c r="E51" t="n">
+        <v>373.23</v>
+      </c>
+      <c r="F51" t="n">
+        <v>373.23</v>
+      </c>
+      <c r="G51" t="n">
+        <v>357.35</v>
+      </c>
+      <c r="H51" t="n">
+        <v>351.67</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J51" t="b">
+        <v>0</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 354.08 &lt;= Upper 373.23)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>04:26:39</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>319.97</v>
+      </c>
+      <c r="E52" t="n">
+        <v>328.06</v>
+      </c>
+      <c r="F52" t="n">
+        <v>328.06</v>
+      </c>
+      <c r="G52" t="n">
+        <v>319.98</v>
+      </c>
+      <c r="H52" t="n">
+        <v>316.73</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="J52" t="b">
+        <v>0</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 319.97 &lt;= Upper 328.06)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>04:26:39</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>499.7</v>
+      </c>
+      <c r="E53" t="n">
+        <v>516.08</v>
+      </c>
+      <c r="F53" t="n">
+        <v>516.08</v>
+      </c>
+      <c r="G53" t="n">
+        <v>500.48</v>
+      </c>
+      <c r="H53" t="n">
+        <v>488.68</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="J53" t="b">
+        <v>0</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 499.70 &lt;= Upper 516.08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>04:26:39</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>616.77</v>
+      </c>
+      <c r="E54" t="n">
+        <v>619.29</v>
+      </c>
+      <c r="F54" t="n">
+        <v>619.29</v>
+      </c>
+      <c r="G54" t="n">
+        <v>589.64</v>
+      </c>
+      <c r="H54" t="n">
+        <v>583.6</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J54" t="b">
+        <v>0</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 616.77 &lt;= Upper 619.29)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>04:26:39</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>258.51</v>
+      </c>
+      <c r="E55" t="n">
+        <v>273.63</v>
+      </c>
+      <c r="F55" t="n">
+        <v>273.63</v>
+      </c>
+      <c r="G55" t="n">
+        <v>258.96</v>
+      </c>
+      <c r="H55" t="n">
+        <v>259.54</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="J55" t="b">
+        <v>0</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 258.96 &lt;= EMA21 259.54)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>04:26:39</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>338.46</v>
+      </c>
+      <c r="E56" t="n">
+        <v>353.14</v>
+      </c>
+      <c r="F56" t="n">
+        <v>353.14</v>
+      </c>
+      <c r="G56" t="n">
+        <v>340.75</v>
+      </c>
+      <c r="H56" t="n">
+        <v>343.59</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="J56" t="b">
+        <v>0</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 340.75 &lt;= EMA21 343.59)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>04:26:39</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>477.57</v>
+      </c>
+      <c r="E57" t="n">
+        <v>505.22</v>
+      </c>
+      <c r="F57" t="n">
+        <v>505.22</v>
+      </c>
+      <c r="G57" t="n">
+        <v>468.28</v>
+      </c>
+      <c r="H57" t="n">
+        <v>475.5</v>
+      </c>
+      <c r="I57" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="J57" t="b">
+        <v>0</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 468.28 &lt;= EMA21 475.50)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>04:26:39</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>78.25</v>
+      </c>
+      <c r="E58" t="n">
+        <v>84.38</v>
+      </c>
+      <c r="F58" t="n">
+        <v>84.38</v>
+      </c>
+      <c r="G58" t="n">
+        <v>80.62</v>
+      </c>
+      <c r="H58" t="n">
+        <v>79.13</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="J58" t="b">
+        <v>0</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 78.25 &lt;= Upper 84.38)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>04:26:39</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>174.33</v>
+      </c>
+      <c r="E59" t="n">
+        <v>187.21</v>
+      </c>
+      <c r="F59" t="n">
+        <v>187.21</v>
+      </c>
+      <c r="G59" t="n">
+        <v>177.88</v>
+      </c>
+      <c r="H59" t="n">
+        <v>171.96</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="J59" t="b">
+        <v>0</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 174.33 &lt;= Upper 187.21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>04:26:39</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>357.89</v>
+      </c>
+      <c r="E60" t="n">
+        <v>424.09</v>
+      </c>
+      <c r="F60" t="n">
+        <v>424.09</v>
+      </c>
+      <c r="G60" t="n">
+        <v>365.27</v>
+      </c>
+      <c r="H60" t="n">
+        <v>374.12</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="J60" t="b">
+        <v>0</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 365.27 &lt;= EMA21 374.12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>04:26:39</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>COIN</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>184.64</v>
+      </c>
+      <c r="E61" t="n">
+        <v>204.15</v>
+      </c>
+      <c r="F61" t="n">
+        <v>204.15</v>
+      </c>
+      <c r="G61" t="n">
+        <v>181.51</v>
+      </c>
+      <c r="H61" t="n">
+        <v>173.86</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="J61" t="b">
+        <v>0</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 184.64 &lt;= Upper 204.15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>04:26:39</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ARM</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>252.09</v>
+      </c>
+      <c r="E62" t="n">
+        <v>282.59</v>
+      </c>
+      <c r="F62" t="n">
+        <v>282.59</v>
+      </c>
+      <c r="G62" t="n">
+        <v>244.99</v>
+      </c>
+      <c r="H62" t="n">
+        <v>252.3</v>
+      </c>
+      <c r="I62" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="J62" t="b">
+        <v>0</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>EMA_BEARISH (EMA9 244.99 &lt;= EMA21 252.30)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>04:26:39</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>75.76000000000001</v>
+      </c>
+      <c r="E63" t="n">
+        <v>80.47</v>
+      </c>
+      <c r="F63" t="n">
+        <v>80.47</v>
+      </c>
+      <c r="G63" t="n">
+        <v>76.54000000000001</v>
+      </c>
+      <c r="H63" t="n">
+        <v>76.11</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="J63" t="b">
+        <v>0</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 75.76 &lt;= Upper 80.47)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>04:26:39</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>39.59</v>
+      </c>
+      <c r="E64" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="F64" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="G64" t="n">
+        <v>37.67</v>
+      </c>
+      <c r="H64" t="n">
+        <v>36.19</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="J64" t="b">
+        <v>0</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 39.59 &lt;= Upper 41.40)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>04:26:39</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>QCOM</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>168.74</v>
+      </c>
+      <c r="E65" t="n">
+        <v>170.32</v>
+      </c>
+      <c r="F65" t="n">
+        <v>170.32</v>
+      </c>
+      <c r="G65" t="n">
+        <v>166.2</v>
+      </c>
+      <c r="H65" t="n">
+        <v>164.92</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="J65" t="b">
+        <v>0</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>BELOW_BAND (Close 168.74 &lt;= Upper 170.32)</t>
         </is>
       </c>
     </row>
@@ -3219,7 +3907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3368,6 +4056,39 @@
         <v>0</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>04:26:39</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>9828.719999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>9828.719999999999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-171.28</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
